--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA0640E9-7FFF-43A3-B5E7-924F58AB3E1F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2846,24 +2846,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="2" xfId="34" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2917,6 +2899,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -14258,206 +14258,206 @@
       <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="66">
+      <c r="D3" s="85"/>
+      <c r="E3" s="86">
         <v>46314</v>
       </c>
-      <c r="F3" s="66"/>
+      <c r="F3" s="86"/>
     </row>
     <row r="4" spans="1:134" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="68"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="63">
+      <c r="I4" s="81">
         <f>I5</f>
         <v>46314</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="63">
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="81">
         <f>P5</f>
         <v>46321</v>
       </c>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="63">
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="81">
         <f>W5</f>
         <v>46328</v>
       </c>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="63">
+      <c r="X4" s="82"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="81">
         <f>AD5</f>
         <v>46335</v>
       </c>
-      <c r="AE4" s="64"/>
-      <c r="AF4" s="64"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="64"/>
-      <c r="AI4" s="64"/>
-      <c r="AJ4" s="65"/>
-      <c r="AK4" s="63">
+      <c r="AE4" s="82"/>
+      <c r="AF4" s="82"/>
+      <c r="AG4" s="82"/>
+      <c r="AH4" s="82"/>
+      <c r="AI4" s="82"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="81">
         <f>AK5</f>
         <v>46342</v>
       </c>
-      <c r="AL4" s="64"/>
-      <c r="AM4" s="64"/>
-      <c r="AN4" s="64"/>
-      <c r="AO4" s="64"/>
-      <c r="AP4" s="64"/>
-      <c r="AQ4" s="65"/>
-      <c r="AR4" s="63">
+      <c r="AL4" s="82"/>
+      <c r="AM4" s="82"/>
+      <c r="AN4" s="82"/>
+      <c r="AO4" s="82"/>
+      <c r="AP4" s="82"/>
+      <c r="AQ4" s="83"/>
+      <c r="AR4" s="81">
         <f>AR5</f>
         <v>46349</v>
       </c>
-      <c r="AS4" s="64"/>
-      <c r="AT4" s="64"/>
-      <c r="AU4" s="64"/>
-      <c r="AV4" s="64"/>
-      <c r="AW4" s="64"/>
-      <c r="AX4" s="65"/>
-      <c r="AY4" s="63">
+      <c r="AS4" s="82"/>
+      <c r="AT4" s="82"/>
+      <c r="AU4" s="82"/>
+      <c r="AV4" s="82"/>
+      <c r="AW4" s="82"/>
+      <c r="AX4" s="83"/>
+      <c r="AY4" s="81">
         <f>AY5</f>
         <v>46356</v>
       </c>
-      <c r="AZ4" s="64"/>
-      <c r="BA4" s="64"/>
-      <c r="BB4" s="64"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-      <c r="BE4" s="65"/>
-      <c r="BF4" s="63">
+      <c r="AZ4" s="82"/>
+      <c r="BA4" s="82"/>
+      <c r="BB4" s="82"/>
+      <c r="BC4" s="82"/>
+      <c r="BD4" s="82"/>
+      <c r="BE4" s="83"/>
+      <c r="BF4" s="81">
         <f>BF5</f>
         <v>46363</v>
       </c>
-      <c r="BG4" s="64"/>
-      <c r="BH4" s="64"/>
-      <c r="BI4" s="64"/>
-      <c r="BJ4" s="64"/>
-      <c r="BK4" s="64"/>
-      <c r="BL4" s="65"/>
-      <c r="BM4" s="63">
+      <c r="BG4" s="82"/>
+      <c r="BH4" s="82"/>
+      <c r="BI4" s="82"/>
+      <c r="BJ4" s="82"/>
+      <c r="BK4" s="82"/>
+      <c r="BL4" s="83"/>
+      <c r="BM4" s="81">
         <f>BM5</f>
         <v>46370</v>
       </c>
-      <c r="BN4" s="64"/>
-      <c r="BO4" s="64"/>
-      <c r="BP4" s="64"/>
-      <c r="BQ4" s="64"/>
-      <c r="BR4" s="64"/>
-      <c r="BS4" s="65"/>
-      <c r="BT4" s="63">
+      <c r="BN4" s="82"/>
+      <c r="BO4" s="82"/>
+      <c r="BP4" s="82"/>
+      <c r="BQ4" s="82"/>
+      <c r="BR4" s="82"/>
+      <c r="BS4" s="83"/>
+      <c r="BT4" s="81">
         <f t="shared" ref="BT4" si="0">BT5</f>
         <v>46377</v>
       </c>
-      <c r="BU4" s="64"/>
-      <c r="BV4" s="64"/>
-      <c r="BW4" s="64"/>
-      <c r="BX4" s="64"/>
-      <c r="BY4" s="64"/>
-      <c r="BZ4" s="65"/>
-      <c r="CA4" s="63">
+      <c r="BU4" s="82"/>
+      <c r="BV4" s="82"/>
+      <c r="BW4" s="82"/>
+      <c r="BX4" s="82"/>
+      <c r="BY4" s="82"/>
+      <c r="BZ4" s="83"/>
+      <c r="CA4" s="81">
         <f t="shared" ref="CA4" si="1">CA5</f>
         <v>46384</v>
       </c>
-      <c r="CB4" s="64"/>
-      <c r="CC4" s="64"/>
-      <c r="CD4" s="64"/>
-      <c r="CE4" s="64"/>
-      <c r="CF4" s="64"/>
-      <c r="CG4" s="65"/>
-      <c r="CH4" s="63">
+      <c r="CB4" s="82"/>
+      <c r="CC4" s="82"/>
+      <c r="CD4" s="82"/>
+      <c r="CE4" s="82"/>
+      <c r="CF4" s="82"/>
+      <c r="CG4" s="83"/>
+      <c r="CH4" s="81">
         <f t="shared" ref="CH4" si="2">CH5</f>
         <v>46391</v>
       </c>
-      <c r="CI4" s="64"/>
-      <c r="CJ4" s="64"/>
-      <c r="CK4" s="64"/>
-      <c r="CL4" s="64"/>
-      <c r="CM4" s="64"/>
-      <c r="CN4" s="65"/>
-      <c r="CO4" s="63">
+      <c r="CI4" s="82"/>
+      <c r="CJ4" s="82"/>
+      <c r="CK4" s="82"/>
+      <c r="CL4" s="82"/>
+      <c r="CM4" s="82"/>
+      <c r="CN4" s="83"/>
+      <c r="CO4" s="81">
         <f t="shared" ref="CO4" si="3">CO5</f>
         <v>46398</v>
       </c>
-      <c r="CP4" s="64"/>
-      <c r="CQ4" s="64"/>
-      <c r="CR4" s="64"/>
-      <c r="CS4" s="64"/>
-      <c r="CT4" s="64"/>
-      <c r="CU4" s="65"/>
-      <c r="CV4" s="63">
+      <c r="CP4" s="82"/>
+      <c r="CQ4" s="82"/>
+      <c r="CR4" s="82"/>
+      <c r="CS4" s="82"/>
+      <c r="CT4" s="82"/>
+      <c r="CU4" s="83"/>
+      <c r="CV4" s="81">
         <f>CV5</f>
         <v>46405</v>
       </c>
-      <c r="CW4" s="64"/>
-      <c r="CX4" s="64"/>
-      <c r="CY4" s="64"/>
-      <c r="CZ4" s="64"/>
-      <c r="DA4" s="64"/>
-      <c r="DB4" s="65"/>
-      <c r="DC4" s="63">
+      <c r="CW4" s="82"/>
+      <c r="CX4" s="82"/>
+      <c r="CY4" s="82"/>
+      <c r="CZ4" s="82"/>
+      <c r="DA4" s="82"/>
+      <c r="DB4" s="83"/>
+      <c r="DC4" s="81">
         <f>DC5</f>
         <v>46412</v>
       </c>
-      <c r="DD4" s="64"/>
-      <c r="DE4" s="64"/>
-      <c r="DF4" s="64"/>
-      <c r="DG4" s="64"/>
-      <c r="DH4" s="64"/>
-      <c r="DI4" s="65"/>
-      <c r="DJ4" s="63">
+      <c r="DD4" s="82"/>
+      <c r="DE4" s="82"/>
+      <c r="DF4" s="82"/>
+      <c r="DG4" s="82"/>
+      <c r="DH4" s="82"/>
+      <c r="DI4" s="83"/>
+      <c r="DJ4" s="81">
         <f t="shared" ref="DJ4" si="4">DJ5</f>
         <v>46419</v>
       </c>
-      <c r="DK4" s="64"/>
-      <c r="DL4" s="64"/>
-      <c r="DM4" s="64"/>
-      <c r="DN4" s="64"/>
-      <c r="DO4" s="64"/>
-      <c r="DP4" s="65"/>
-      <c r="DQ4" s="63">
+      <c r="DK4" s="82"/>
+      <c r="DL4" s="82"/>
+      <c r="DM4" s="82"/>
+      <c r="DN4" s="82"/>
+      <c r="DO4" s="82"/>
+      <c r="DP4" s="83"/>
+      <c r="DQ4" s="81">
         <f t="shared" ref="DQ4" si="5">DQ5</f>
         <v>46426</v>
       </c>
-      <c r="DR4" s="64"/>
-      <c r="DS4" s="64"/>
-      <c r="DT4" s="64"/>
-      <c r="DU4" s="64"/>
-      <c r="DV4" s="64"/>
-      <c r="DW4" s="65"/>
-      <c r="DX4" s="63">
+      <c r="DR4" s="82"/>
+      <c r="DS4" s="82"/>
+      <c r="DT4" s="82"/>
+      <c r="DU4" s="82"/>
+      <c r="DV4" s="82"/>
+      <c r="DW4" s="83"/>
+      <c r="DX4" s="81">
         <f t="shared" ref="DX4" si="6">DX5</f>
         <v>46433</v>
       </c>
-      <c r="DY4" s="64"/>
-      <c r="DZ4" s="64"/>
-      <c r="EA4" s="64"/>
-      <c r="EB4" s="64"/>
-      <c r="EC4" s="64"/>
-      <c r="ED4" s="65"/>
+      <c r="DY4" s="82"/>
+      <c r="DZ4" s="82"/>
+      <c r="EA4" s="82"/>
+      <c r="EB4" s="82"/>
+      <c r="EC4" s="82"/>
+      <c r="ED4" s="83"/>
     </row>
     <row r="5" spans="1:134" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -16075,7 +16075,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="49">
         <f>プロジェクトの開始</f>
@@ -16228,7 +16228,7 @@
         <v>38</v>
       </c>
       <c r="D12" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="49">
         <f>F11</f>
@@ -16379,7 +16379,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="49">
         <f>F12</f>
@@ -16672,7 +16672,7 @@
         <v>38</v>
       </c>
       <c r="D15" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="49">
         <f>プロジェクトの開始</f>
@@ -16823,7 +16823,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="49">
         <f>F15</f>
@@ -17861,7 +17861,7 @@
     </row>
     <row r="23" spans="1:134" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="77" t="s">
         <v>245</v>
       </c>
       <c r="C23" s="13" t="s">
@@ -21243,7 +21243,7 @@
       <c r="ED45" s="4"/>
     </row>
     <row r="46" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="83" t="s">
+      <c r="B46" s="77" t="s">
         <v>226</v>
       </c>
       <c r="C46" s="13" t="s">
@@ -22127,7 +22127,7 @@
       <c r="ED51" s="4"/>
     </row>
     <row r="52" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="83" t="s">
+      <c r="B52" s="77" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="13" t="s">
@@ -22277,7 +22277,7 @@
       <c r="ED52" s="4"/>
     </row>
     <row r="53" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="83" t="s">
+      <c r="B53" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C53" s="13" t="s">
@@ -24045,7 +24045,7 @@
       <c r="ED64" s="4"/>
     </row>
     <row r="65" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="83" t="s">
+      <c r="B65" s="77" t="s">
         <v>228</v>
       </c>
       <c r="C65" s="13" t="s">
@@ -24195,7 +24195,7 @@
       <c r="ED65" s="4"/>
     </row>
     <row r="66" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="83" t="s">
+      <c r="B66" s="77" t="s">
         <v>229</v>
       </c>
       <c r="C66" s="13" t="s">
@@ -24345,7 +24345,7 @@
       <c r="ED66" s="4"/>
     </row>
     <row r="67" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="83" t="s">
+      <c r="B67" s="77" t="s">
         <v>233</v>
       </c>
       <c r="C67" s="13" t="s">
@@ -25221,7 +25221,7 @@
       <c r="ED72" s="4"/>
     </row>
     <row r="73" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="83" t="s">
+      <c r="B73" s="77" t="s">
         <v>247</v>
       </c>
       <c r="C73" s="13" t="s">
@@ -25371,7 +25371,7 @@
       <c r="ED73" s="4"/>
     </row>
     <row r="74" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="83" t="s">
+      <c r="B74" s="77" t="s">
         <v>248</v>
       </c>
       <c r="C74" s="13" t="s">
@@ -25805,7 +25805,7 @@
       <c r="ED76" s="4"/>
     </row>
     <row r="77" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="83" t="s">
+      <c r="B77" s="77" t="s">
         <v>231</v>
       </c>
       <c r="C77" s="13" t="s">
@@ -25955,7 +25955,7 @@
       <c r="ED77" s="4"/>
     </row>
     <row r="78" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="83" t="s">
+      <c r="B78" s="77" t="s">
         <v>232</v>
       </c>
       <c r="C78" s="13" t="s">
@@ -26105,7 +26105,7 @@
       <c r="ED78" s="4"/>
     </row>
     <row r="79" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="83" t="s">
+      <c r="B79" s="77" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="13" t="s">
@@ -27423,7 +27423,7 @@
       <c r="ED87" s="4"/>
     </row>
     <row r="88" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="83" t="s">
+      <c r="B88" s="77" t="s">
         <v>235</v>
       </c>
       <c r="C88" s="13" t="s">
@@ -27573,7 +27573,7 @@
       <c r="ED88" s="4"/>
     </row>
     <row r="89" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="83" t="s">
+      <c r="B89" s="77" t="s">
         <v>236</v>
       </c>
       <c r="C89" s="13" t="s">
@@ -27723,7 +27723,7 @@
       <c r="ED89" s="4"/>
     </row>
     <row r="90" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="83" t="s">
+      <c r="B90" s="77" t="s">
         <v>237</v>
       </c>
       <c r="C90" s="13" t="s">
@@ -28607,7 +28607,7 @@
       <c r="ED95" s="4"/>
     </row>
     <row r="96" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="83" t="s">
+      <c r="B96" s="77" t="s">
         <v>249</v>
       </c>
       <c r="C96" s="13" t="s">
@@ -29035,7 +29035,7 @@
       <c r="ED98" s="4"/>
     </row>
     <row r="99" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="83" t="s">
+      <c r="B99" s="77" t="s">
         <v>238</v>
       </c>
       <c r="C99" s="13" t="s">
@@ -29185,7 +29185,7 @@
       <c r="ED99" s="4"/>
     </row>
     <row r="100" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="83" t="s">
+      <c r="B100" s="77" t="s">
         <v>239</v>
       </c>
       <c r="C100" s="13" t="s">
@@ -29335,7 +29335,7 @@
       <c r="ED100" s="4"/>
     </row>
     <row r="101" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="83" t="s">
+      <c r="B101" s="77" t="s">
         <v>240</v>
       </c>
       <c r="C101" s="13" t="s">
@@ -30353,7 +30353,7 @@
       <c r="ED107" s="4"/>
     </row>
     <row r="108" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="83" t="s">
+      <c r="B108" s="77" t="s">
         <v>241</v>
       </c>
       <c r="C108" s="13" t="s">
@@ -30503,7 +30503,7 @@
       <c r="ED108" s="4"/>
     </row>
     <row r="109" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="83" t="s">
+      <c r="B109" s="77" t="s">
         <v>242</v>
       </c>
       <c r="C109" s="13" t="s">
@@ -30653,7 +30653,7 @@
       <c r="ED109" s="4"/>
     </row>
     <row r="110" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="83" t="s">
+      <c r="B110" s="77" t="s">
         <v>243</v>
       </c>
       <c r="C110" s="13" t="s">
@@ -31971,7 +31971,7 @@
       <c r="ED118" s="4"/>
     </row>
     <row r="119" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="83" t="s">
+      <c r="B119" s="77" t="s">
         <v>252</v>
       </c>
       <c r="C119" s="13" t="s">
@@ -32121,7 +32121,7 @@
       <c r="ED119" s="4"/>
     </row>
     <row r="120" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="83" t="s">
+      <c r="B120" s="77" t="s">
         <v>253</v>
       </c>
       <c r="C120" s="13" t="s">
@@ -32271,7 +32271,7 @@
       <c r="ED120" s="4"/>
     </row>
     <row r="121" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="83" t="s">
+      <c r="B121" s="77" t="s">
         <v>254</v>
       </c>
       <c r="C121" s="13" t="s">
@@ -32855,7 +32855,7 @@
       <c r="ED124" s="4"/>
     </row>
     <row r="125" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="83" t="s">
+      <c r="B125" s="77" t="s">
         <v>255</v>
       </c>
       <c r="C125" s="13" t="s">
@@ -33005,7 +33005,7 @@
       <c r="ED125" s="4"/>
     </row>
     <row r="126" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="83" t="s">
+      <c r="B126" s="77" t="s">
         <v>264</v>
       </c>
       <c r="C126" s="13" t="s">
@@ -33155,7 +33155,7 @@
       <c r="ED126" s="4"/>
     </row>
     <row r="127" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B127" s="83" t="s">
+      <c r="B127" s="77" t="s">
         <v>265</v>
       </c>
       <c r="C127" s="13" t="s">
@@ -33305,7 +33305,7 @@
       <c r="ED127" s="4"/>
     </row>
     <row r="128" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="83" t="s">
+      <c r="B128" s="77" t="s">
         <v>266</v>
       </c>
       <c r="C128" s="13" t="s">
@@ -33455,7 +33455,7 @@
       <c r="ED128" s="4"/>
     </row>
     <row r="129" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="83" t="s">
+      <c r="B129" s="77" t="s">
         <v>256</v>
       </c>
       <c r="C129" s="13" t="s">
@@ -33605,7 +33605,7 @@
       <c r="ED129" s="4"/>
     </row>
     <row r="130" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="83" t="s">
+      <c r="B130" s="77" t="s">
         <v>259</v>
       </c>
       <c r="C130" s="13" t="s">
@@ -33755,7 +33755,7 @@
       <c r="ED130" s="4"/>
     </row>
     <row r="131" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B131" s="83" t="s">
+      <c r="B131" s="77" t="s">
         <v>260</v>
       </c>
       <c r="C131" s="13" t="s">
@@ -33905,7 +33905,7 @@
       <c r="ED131" s="4"/>
     </row>
     <row r="132" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B132" s="83" t="s">
+      <c r="B132" s="77" t="s">
         <v>257</v>
       </c>
       <c r="C132" s="13" t="s">
@@ -34055,7 +34055,7 @@
       <c r="ED132" s="4"/>
     </row>
     <row r="133" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B133" s="83" t="s">
+      <c r="B133" s="77" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="13" t="s">
@@ -34205,7 +34205,7 @@
       <c r="ED133" s="4"/>
     </row>
     <row r="134" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B134" s="83" t="s">
+      <c r="B134" s="77" t="s">
         <v>262</v>
       </c>
       <c r="C134" s="13" t="s">
@@ -34355,7 +34355,7 @@
       <c r="ED134" s="4"/>
     </row>
     <row r="135" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B135" s="83" t="s">
+      <c r="B135" s="77" t="s">
         <v>263</v>
       </c>
       <c r="C135" s="13" t="s">
@@ -34647,7 +34647,7 @@
       <c r="ED136" s="4"/>
     </row>
     <row r="137" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="83" t="s">
+      <c r="B137" s="77" t="s">
         <v>247</v>
       </c>
       <c r="C137" s="13" t="s">
@@ -34797,7 +34797,7 @@
       <c r="ED137" s="4"/>
     </row>
     <row r="138" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="83" t="s">
+      <c r="B138" s="77" t="s">
         <v>248</v>
       </c>
       <c r="C138" s="13" t="s">
@@ -47344,7 +47344,7 @@
         <f>F222</f>
         <v>46406</v>
       </c>
-      <c r="F223" s="84">
+      <c r="F223" s="78">
         <f>E223</f>
         <v>46406</v>
       </c>
@@ -51451,15 +51451,15 @@
       <c r="ED250" s="4"/>
     </row>
     <row r="251" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B251" s="69" t="s">
+      <c r="B251" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="C251" s="70" t="s">
+      <c r="C251" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D251" s="71"/>
-      <c r="E251" s="72"/>
-      <c r="F251" s="72"/>
+      <c r="D251" s="65"/>
+      <c r="E251" s="66"/>
+      <c r="F251" s="66"/>
       <c r="G251" s="29"/>
       <c r="H251" s="29" t="str">
         <f t="shared" si="76"/>
@@ -51593,15 +51593,15 @@
       <c r="ED251" s="4"/>
     </row>
     <row r="252" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B252" s="76" t="s">
+      <c r="B252" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="C252" s="73" t="s">
+      <c r="C252" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="D252" s="74"/>
-      <c r="E252" s="75"/>
-      <c r="F252" s="75"/>
+      <c r="D252" s="68"/>
+      <c r="E252" s="69"/>
+      <c r="F252" s="69"/>
       <c r="G252" s="29"/>
       <c r="H252" s="29" t="str">
         <f t="shared" si="76"/>
@@ -51735,15 +51735,15 @@
       <c r="ED252" s="4"/>
     </row>
     <row r="253" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B253" s="80" t="s">
+      <c r="B253" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="C253" s="77" t="s">
+      <c r="C253" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D253" s="78"/>
-      <c r="E253" s="79"/>
-      <c r="F253" s="79"/>
+      <c r="D253" s="72"/>
+      <c r="E253" s="73"/>
+      <c r="F253" s="73"/>
       <c r="G253" s="29"/>
       <c r="H253" s="29" t="str">
         <f t="shared" si="76"/>
@@ -52177,15 +52177,15 @@
       <c r="ED255" s="4"/>
     </row>
     <row r="256" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B256" s="80" t="s">
+      <c r="B256" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="C256" s="77" t="s">
+      <c r="C256" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D256" s="78"/>
-      <c r="E256" s="79"/>
-      <c r="F256" s="79"/>
+      <c r="D256" s="72"/>
+      <c r="E256" s="73"/>
+      <c r="F256" s="73"/>
       <c r="G256" s="29"/>
       <c r="H256" s="29" t="str">
         <f t="shared" si="76"/>
@@ -52319,7 +52319,7 @@
       <c r="ED256" s="4"/>
     </row>
     <row r="257" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B257" s="81" t="s">
+      <c r="B257" s="75" t="s">
         <v>209</v>
       </c>
       <c r="C257" s="14" t="s">
@@ -52469,7 +52469,7 @@
       <c r="ED257" s="4"/>
     </row>
     <row r="258" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B258" s="85" t="s">
+      <c r="B258" s="79" t="s">
         <v>207</v>
       </c>
       <c r="C258" s="14" t="s">
@@ -52619,15 +52619,15 @@
       <c r="ED258" s="4"/>
     </row>
     <row r="259" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B259" s="80" t="s">
+      <c r="B259" s="74" t="s">
         <v>210</v>
       </c>
-      <c r="C259" s="77" t="s">
+      <c r="C259" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D259" s="78"/>
-      <c r="E259" s="79"/>
-      <c r="F259" s="79"/>
+      <c r="D259" s="72"/>
+      <c r="E259" s="73"/>
+      <c r="F259" s="73"/>
       <c r="G259" s="29"/>
       <c r="H259" s="29" t="str">
         <f t="shared" si="76"/>
@@ -52761,7 +52761,7 @@
       <c r="ED259" s="4"/>
     </row>
     <row r="260" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B260" s="81" t="s">
+      <c r="B260" s="75" t="s">
         <v>211</v>
       </c>
       <c r="C260" s="14" t="s">
@@ -52911,7 +52911,7 @@
       <c r="ED260" s="4"/>
     </row>
     <row r="261" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B261" s="85" t="s">
+      <c r="B261" s="79" t="s">
         <v>207</v>
       </c>
       <c r="C261" s="14" t="s">
@@ -53061,15 +53061,15 @@
       <c r="ED261" s="4"/>
     </row>
     <row r="262" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B262" s="76" t="s">
+      <c r="B262" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="C262" s="73" t="s">
+      <c r="C262" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="D262" s="74"/>
-      <c r="E262" s="75"/>
-      <c r="F262" s="75"/>
+      <c r="D262" s="68"/>
+      <c r="E262" s="69"/>
+      <c r="F262" s="69"/>
       <c r="G262" s="29"/>
       <c r="H262" s="29" t="str">
         <f t="shared" si="76"/>
@@ -53203,15 +53203,15 @@
       <c r="ED262" s="4"/>
     </row>
     <row r="263" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B263" s="82" t="s">
+      <c r="B263" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="C263" s="77" t="s">
+      <c r="C263" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D263" s="78"/>
-      <c r="E263" s="79"/>
-      <c r="F263" s="79"/>
+      <c r="D263" s="72"/>
+      <c r="E263" s="73"/>
+      <c r="F263" s="73"/>
       <c r="G263" s="29"/>
       <c r="H263" s="29" t="str">
         <f t="shared" si="76"/>
@@ -53345,7 +53345,7 @@
       <c r="ED263" s="4"/>
     </row>
     <row r="264" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B264" s="81" t="s">
+      <c r="B264" s="75" t="s">
         <v>214</v>
       </c>
       <c r="C264" s="14" t="s">
@@ -53495,15 +53495,15 @@
       <c r="ED264" s="4"/>
     </row>
     <row r="265" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B265" s="80" t="s">
+      <c r="B265" s="74" t="s">
         <v>215</v>
       </c>
-      <c r="C265" s="77" t="s">
+      <c r="C265" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D265" s="78"/>
-      <c r="E265" s="79"/>
-      <c r="F265" s="79"/>
+      <c r="D265" s="72"/>
+      <c r="E265" s="73"/>
+      <c r="F265" s="73"/>
       <c r="G265" s="29"/>
       <c r="H265" s="29" t="str">
         <f t="shared" si="76"/>
@@ -53637,7 +53637,7 @@
       <c r="ED265" s="4"/>
     </row>
     <row r="266" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B266" s="81" t="s">
+      <c r="B266" s="75" t="s">
         <v>216</v>
       </c>
       <c r="C266" s="14" t="s">
@@ -53787,15 +53787,15 @@
       <c r="ED266" s="4"/>
     </row>
     <row r="267" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B267" s="82" t="s">
+      <c r="B267" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C267" s="77" t="s">
+      <c r="C267" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D267" s="78"/>
-      <c r="E267" s="79"/>
-      <c r="F267" s="79"/>
+      <c r="D267" s="72"/>
+      <c r="E267" s="73"/>
+      <c r="F267" s="73"/>
       <c r="G267" s="29"/>
       <c r="H267" s="29" t="str">
         <f t="shared" si="76"/>
@@ -53929,7 +53929,7 @@
       <c r="ED267" s="4"/>
     </row>
     <row r="268" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B268" s="81" t="s">
+      <c r="B268" s="75" t="s">
         <v>217</v>
       </c>
       <c r="C268" s="14" t="s">
@@ -54079,7 +54079,7 @@
       <c r="ED268" s="4"/>
     </row>
     <row r="269" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B269" s="81" t="s">
+      <c r="B269" s="75" t="s">
         <v>220</v>
       </c>
       <c r="C269" s="14" t="s">
@@ -54229,15 +54229,15 @@
       <c r="ED269" s="4"/>
     </row>
     <row r="270" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B270" s="80" t="s">
+      <c r="B270" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="C270" s="77" t="s">
+      <c r="C270" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D270" s="78"/>
-      <c r="E270" s="79"/>
-      <c r="F270" s="79"/>
+      <c r="D270" s="72"/>
+      <c r="E270" s="73"/>
+      <c r="F270" s="73"/>
       <c r="G270" s="29"/>
       <c r="H270" s="29" t="str">
         <f t="shared" si="76"/>
@@ -54371,7 +54371,7 @@
       <c r="ED270" s="4"/>
     </row>
     <row r="271" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B271" s="81" t="s">
+      <c r="B271" s="75" t="s">
         <v>219</v>
       </c>
       <c r="C271" s="14" t="s">
@@ -54521,15 +54521,15 @@
       <c r="ED271" s="4"/>
     </row>
     <row r="272" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B272" s="80" t="s">
+      <c r="B272" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="C272" s="77" t="s">
+      <c r="C272" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D272" s="78"/>
-      <c r="E272" s="79"/>
-      <c r="F272" s="79"/>
+      <c r="D272" s="72"/>
+      <c r="E272" s="73"/>
+      <c r="F272" s="73"/>
       <c r="G272" s="29"/>
       <c r="H272" s="29" t="str">
         <f t="shared" si="76"/>
@@ -54663,7 +54663,7 @@
       <c r="ED272" s="4"/>
     </row>
     <row r="273" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B273" s="81" t="s">
+      <c r="B273" s="75" t="s">
         <v>222</v>
       </c>
       <c r="C273" s="14" t="s">
@@ -54813,15 +54813,15 @@
       <c r="ED273" s="4"/>
     </row>
     <row r="274" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B274" s="80" t="s">
+      <c r="B274" s="74" t="s">
         <v>268</v>
       </c>
-      <c r="C274" s="77" t="s">
+      <c r="C274" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="D274" s="78"/>
-      <c r="E274" s="79"/>
-      <c r="F274" s="79"/>
+      <c r="D274" s="72"/>
+      <c r="E274" s="73"/>
+      <c r="F274" s="73"/>
       <c r="G274" s="29"/>
       <c r="H274" s="29" t="str">
         <f t="shared" si="76"/>
@@ -54955,7 +54955,7 @@
       <c r="ED274" s="4"/>
     </row>
     <row r="275" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B275" s="86" t="s">
+      <c r="B275" s="80" t="s">
         <v>247</v>
       </c>
       <c r="C275" s="14" t="s">
@@ -54974,7 +54974,7 @@
       </c>
       <c r="G275" s="29"/>
       <c r="H275" s="29">
-        <f t="shared" ref="H275:I276" si="77">IF(OR(ISBLANK(タスク_開始),ISBLANK(タスク_終了)),"",タスク_終了-タスク_開始+1)</f>
+        <f t="shared" ref="H275:H276" si="77">IF(OR(ISBLANK(タスク_開始),ISBLANK(タスク_終了)),"",タスク_終了-タスク_開始+1)</f>
         <v>3</v>
       </c>
       <c r="I275" s="4"/>
@@ -55105,7 +55105,7 @@
       <c r="ED275" s="4"/>
     </row>
     <row r="276" spans="2:134" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B276" s="86" t="s">
+      <c r="B276" s="80" t="s">
         <v>269</v>
       </c>
       <c r="C276" s="14" t="s">
@@ -55263,27 +55263,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="DJ4:DP4"/>
-    <mergeCell ref="DQ4:DW4"/>
-    <mergeCell ref="DX4:ED4"/>
-    <mergeCell ref="BM4:BS4"/>
-    <mergeCell ref="BT4:BZ4"/>
-    <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="CH4:CN4"/>
-    <mergeCell ref="CO4:CU4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
+    <mergeCell ref="BM4:BS4"/>
+    <mergeCell ref="BT4:BZ4"/>
+    <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="CH4:CN4"/>
+    <mergeCell ref="CO4:CU4"/>
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
+    <mergeCell ref="DJ4:DP4"/>
+    <mergeCell ref="DQ4:DW4"/>
+    <mergeCell ref="DX4:ED4"/>
   </mergeCells>
   <phoneticPr fontId="28"/>
   <conditionalFormatting sqref="D7:D13 D38 D40 D42 D251:D255 D261 D44">
@@ -62289,6 +62289,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -62576,36 +62605,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -62624,24 +62644,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA0640E9-7FFF-43A3-B5E7-924F58AB3E1F}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E5BCCA-75BA-4621-8052-7A3003A36503}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2909,14 +2909,14 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -14258,23 +14258,23 @@
       <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="86">
+      <c r="D3" s="86"/>
+      <c r="E3" s="84">
         <v>46314</v>
       </c>
-      <c r="F3" s="86"/>
+      <c r="F3" s="84"/>
     </row>
     <row r="4" spans="1:134" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="85"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="3">
         <v>1</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="30">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="49">
         <f>F16+1</f>
@@ -55263,27 +55263,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
+    <mergeCell ref="DJ4:DP4"/>
+    <mergeCell ref="DQ4:DW4"/>
+    <mergeCell ref="DX4:ED4"/>
+    <mergeCell ref="BM4:BS4"/>
+    <mergeCell ref="BT4:BZ4"/>
+    <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="CH4:CN4"/>
+    <mergeCell ref="CO4:CU4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="BM4:BS4"/>
-    <mergeCell ref="BT4:BZ4"/>
-    <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="CH4:CN4"/>
-    <mergeCell ref="CO4:CU4"/>
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="DJ4:DP4"/>
-    <mergeCell ref="DQ4:DW4"/>
-    <mergeCell ref="DX4:ED4"/>
   </mergeCells>
   <phoneticPr fontId="28"/>
   <conditionalFormatting sqref="D7:D13 D38 D40 D42 D251:D255 D261 D44">
@@ -62289,35 +62289,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -62605,27 +62576,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -62644,4 +62624,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E5BCCA-75BA-4621-8052-7A3003A36503}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B4197B-1760-42DE-80F3-7BBF72CA9740}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17415,7 +17415,7 @@
         <v>38</v>
       </c>
       <c r="D20" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20" s="49">
         <f>F18</f>
@@ -17566,7 +17566,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21" s="49">
         <f>F20</f>
@@ -17717,7 +17717,7 @@
         <v>38</v>
       </c>
       <c r="D22" s="30">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="49">
         <f>F20</f>

--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -2909,14 +2909,14 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -14258,23 +14258,23 @@
       <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="86"/>
-      <c r="E3" s="84">
+      <c r="D3" s="85"/>
+      <c r="E3" s="86">
         <v>46314</v>
       </c>
-      <c r="F3" s="84"/>
+      <c r="F3" s="86"/>
     </row>
     <row r="4" spans="1:134" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="86"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="3">
         <v>1</v>
       </c>
@@ -55263,27 +55263,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="DJ4:DP4"/>
-    <mergeCell ref="DQ4:DW4"/>
-    <mergeCell ref="DX4:ED4"/>
-    <mergeCell ref="BM4:BS4"/>
-    <mergeCell ref="BT4:BZ4"/>
-    <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="CH4:CN4"/>
-    <mergeCell ref="CO4:CU4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
+    <mergeCell ref="BM4:BS4"/>
+    <mergeCell ref="BT4:BZ4"/>
+    <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="CH4:CN4"/>
+    <mergeCell ref="CO4:CU4"/>
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
+    <mergeCell ref="DJ4:DP4"/>
+    <mergeCell ref="DQ4:DW4"/>
+    <mergeCell ref="DX4:ED4"/>
   </mergeCells>
   <phoneticPr fontId="28"/>
   <conditionalFormatting sqref="D7:D13 D38 D40 D42 D251:D255 D261 D44">
@@ -62289,6 +62289,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -62576,36 +62605,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -62624,24 +62644,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B4197B-1760-42DE-80F3-7BBF72CA9740}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214A8CB4-7A78-4F9B-8A71-F126FFF49CC7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17717,7 +17717,7 @@
         <v>38</v>
       </c>
       <c r="D22" s="30">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" s="49">
         <f>F20</f>
@@ -17868,7 +17868,7 @@
         <v>38</v>
       </c>
       <c r="D23" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E23" s="49">
         <f>F21</f>
@@ -18019,7 +18019,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="49">
         <f>E23</f>

--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214A8CB4-7A78-4F9B-8A71-F126FFF49CC7}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C33CCB5-76E0-4E7E-A454-939D4765B58C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16075,7 +16075,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E11" s="49">
         <f>プロジェクトの開始</f>
@@ -16228,7 +16228,7 @@
         <v>38</v>
       </c>
       <c r="D12" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="49">
         <f>F11</f>
@@ -16379,7 +16379,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E13" s="49">
         <f>F12</f>
@@ -18748,7 +18748,7 @@
         <v>38</v>
       </c>
       <c r="D29" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="49">
         <f>F26</f>
@@ -18898,7 +18898,7 @@
         <v>38</v>
       </c>
       <c r="D30" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="49">
         <f>F29</f>
@@ -19048,7 +19048,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="49">
         <f>E30</f>

--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C33CCB5-76E0-4E7E-A454-939D4765B58C}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84534620-B4A3-4ED0-AD70-CD53E189314C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17119,7 +17119,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="30">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" s="49">
         <f>F16+1</f>
@@ -18314,7 +18314,7 @@
         <v>38</v>
       </c>
       <c r="D26" s="30">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E26" s="49">
         <f>F24</f>
@@ -19048,7 +19048,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E31" s="49">
         <f>E30</f>
@@ -19198,7 +19198,7 @@
         <v>38</v>
       </c>
       <c r="D32" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="49">
         <f>F31</f>
@@ -19348,7 +19348,7 @@
         <v>38</v>
       </c>
       <c r="D33" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="49">
         <f>E32</f>

--- a/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
+++ b/3DLv3/Plan/ギャラクシーシューター（仮）.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84534620-B4A3-4ED0-AD70-CD53E189314C}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{29EE4739-519B-4E93-A7DE-97C18007F75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED56CBA-70E8-4D2F-ABF6-D51F6A414519}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19782,7 +19782,7 @@
         <v>38</v>
       </c>
       <c r="D36" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="49">
         <f>F33</f>
@@ -21834,7 +21834,7 @@
         <v>38</v>
       </c>
       <c r="D50" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E50" s="49">
         <f>F33</f>
@@ -21984,7 +21984,7 @@
         <v>38</v>
       </c>
       <c r="D51" s="30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E51" s="49">
         <f>F50</f>
